--- a/social_media_marketing_forms/031_social_media_content_request_form--social_media_marketing_forms.xlsx
+++ b/social_media_marketing_forms/031_social_media_content_request_form--social_media_marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'post'}</t>
+          <t>post</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Post'}</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'story'}</t>
+          <t>story</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Story'}</t>
+          <t>Story</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'reels'}</t>
+          <t>reels</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Reels'}</t>
+          <t>Reels</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'tag_1'}</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 1'}</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'tag_2'}</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 2'}</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'tag_3'}</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 3'}</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'social_media_marketing_forms'}</t>
+          <t>social_media_marketing_forms</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media Marketing Forms'}</t>
+          <t>Social Media Marketing Forms</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'031_social_media_content_request_form--social_media_marketing_forms'}</t>
+          <t>031_social_media_content_request_form--social_media_marketing_forms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '031_social_media_content_request_form--social_media_marketing_forms'}</t>
+          <t>031 social media content request form--social media marketing forms</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
